--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC1559F-DD70-4F1D-B20B-C332EDE3E2BC}"/>
+  <xr:revisionPtr revIDLastSave="529" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90600344-6E26-4DCF-BD19-07F1D41250F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Canfod papur ffug, lladd bacteria, lliw Haul.</t>
+  </si>
+  <si>
+    <t>1.5 ton</t>
+  </si>
+  <si>
+    <t>3 ton</t>
   </si>
 </sst>
 </file>
@@ -353,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -361,16 +367,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,7 +593,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.54296875" customWidth="1"/>
@@ -634,8 +638,8 @@
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
-        <v>1.5</v>
+      <c r="B4" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>41</v>
@@ -646,8 +650,8 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1">
-        <v>3</v>
+      <c r="B5" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>41</v>
@@ -946,20 +950,16 @@
       <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="529" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90600344-6E26-4DCF-BD19-07F1D41250F4}"/>
+  <xr:revisionPtr revIDLastSave="533" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C08E9B-FF8A-473F-89EB-8F2936053952}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,9 +208,6 @@
     <t>Rhowch enghraifft o donnau arhydol.</t>
   </si>
   <si>
-    <t>Rhestrwch y priodwedau sy'n gyffredin i bob ton em.</t>
-  </si>
-  <si>
     <t>Mae pob ton em yn don ardaws. &lt;br&gt;&lt;br&gt; Mae pob ton em yn teithio ar yr un cyflymder mewn gwactod. &lt;br&gt;&lt;br&gt; Mae pob ton em yn trosgwlyddo egni.</t>
   </si>
   <si>
@@ -263,6 +260,9 @@
   </si>
   <si>
     <t>3 ton</t>
+  </si>
+  <si>
+    <t>Rhestrwch y priodweddau sy'n gyffredin i bob ton em.</t>
   </si>
 </sst>
 </file>
@@ -639,7 +639,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>41</v>
@@ -651,7 +651,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>41</v>
@@ -774,44 +774,43 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="7" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -844,10 +843,10 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
@@ -857,67 +856,67 @@
         <v>36</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="C32" s="4"/>
     </row>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C08E9B-FF8A-473F-89EB-8F2936053952}"/>
+  <xr:revisionPtr revIDLastSave="542" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BBC17A7-4B45-4BF8-820F-3585CEF3DEA7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -157,9 +157,6 @@
     <t>Tonnau sain.</t>
   </si>
   <si>
-    <t>Cywir neu Anhywir: mae pob toin em yn teithio ar yr un buanedd mewn gwactod?</t>
-  </si>
-  <si>
     <t>CYWIR</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>Rhowch enghraifft o donnau arhydol.</t>
   </si>
   <si>
-    <t>Mae pob ton em yn don ardaws. &lt;br&gt;&lt;br&gt; Mae pob ton em yn teithio ar yr un cyflymder mewn gwactod. &lt;br&gt;&lt;br&gt; Mae pob ton em yn trosgwlyddo egni.</t>
-  </si>
-  <si>
     <t>Beth yw lloeren geosefydlog?</t>
   </si>
   <si>
@@ -263,6 +257,18 @@
   </si>
   <si>
     <t>Rhestrwch y priodweddau sy'n gyffredin i bob ton em.</t>
+  </si>
+  <si>
+    <t>Mae pob ton em yn don ardaws. &lt;br&gt;&lt;br&gt; Mae pob ton em yn teithio ar yr un cyflymder mewn gwactod. &lt;br&gt;&lt;br&gt; Mae pob ton em yn trosglwyddo egni.</t>
+  </si>
+  <si>
+    <t>Cywir neu Anhywir: mae pob ton em yn teithio ar yr un buanedd mewn gwactod?</t>
+  </si>
+  <si>
+    <t>Beth yw lloeren geocydamseredig?</t>
+  </si>
+  <si>
+    <t>Mae lloeren geocydamseredig yn cymryd 24 awr i wneud orbit o amgylch  y Ddaear felly mae uwchben yr un pwynt unwaith bob 24 awr.</t>
   </si>
 </sst>
 </file>
@@ -639,10 +645,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1"/>
     </row>
@@ -651,10 +657,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1"/>
     </row>
@@ -669,25 +675,25 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -696,7 +702,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -717,19 +723,19 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -765,7 +771,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>33</v>
@@ -794,7 +800,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -802,23 +808,23 @@
         <v>21</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -833,96 +839,100 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
+      <c r="A33" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8"/>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="542" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BBC17A7-4B45-4BF8-820F-3585CEF3DEA7}"/>
+  <xr:revisionPtr revIDLastSave="676" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B719EFD-5DA2-4322-8FBD-8843A66FD33C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="3.5 Priodweddau Tonnau" sheetId="1" r:id="rId1"/>
+    <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
+    <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="117">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -270,12 +271,167 @@
   <si>
     <t>Mae lloeren geocydamseredig yn cymryd 24 awr i wneud orbit o amgylch  y Ddaear felly mae uwchben yr un pwynt unwaith bob 24 awr.</t>
   </si>
+  <si>
+    <t>Beth yw uned cerrynt?</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Beth yw uned foltedd?</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Beth yw uned gwrthiant?</t>
+  </si>
+  <si>
+    <t>Nodweddion_V-I_gwrthydd.png</t>
+  </si>
+  <si>
+    <t>Beth yw enw cydrannau A,B a C?</t>
+  </si>
+  <si>
+    <t>A - cell / batri un cell &lt;br&gt;&lt;br&gt; B - gwrthydd newidiol &lt;br&gt;&lt;br&gt; C - gwrthydd</t>
+  </si>
+  <si>
+    <t>symbol_amedr.png</t>
+  </si>
+  <si>
+    <t>symbol_foltmedr.png</t>
+  </si>
+  <si>
+    <t>Beth yw'r symbol?</t>
+  </si>
+  <si>
+    <t>amedr</t>
+  </si>
+  <si>
+    <t>foltmedr</t>
+  </si>
+  <si>
+    <t>Ym mha safle mae'r amedr, CH neu D?</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Ym mha safle mae'r foltmedr, CH neu D?</t>
+  </si>
+  <si>
+    <t>Ω</t>
+  </si>
+  <si>
+    <t>cylched_paralel.png</t>
+  </si>
+  <si>
+    <t>(a) Cylched cyfres neu paralel?&lt;br&gt;&lt;br&gt;(b) Beth yw'r cerrynt yn X?</t>
+  </si>
+  <si>
+    <t>(a) cylched paralel&lt;br&gt;&lt;br&gt; (b) cerrynt = 0.1 + 0.2 = 0.3 A</t>
+  </si>
+  <si>
+    <t>rheolau_foltedd.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) Beth yw'r foltedd ar draws lamp $L_{2}$ a beth yw'r rheol?&lt;br&gt;&lt;br&gt; (b) Beth yw'r foltedd ar draws lamp $L_{4}$ a beth yw'r rheol? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) 8 V  - cydrannau mewn paralel gyda'r un foltedd &lt;br&gt;&lt;br&gt; (b) 9 V - foltedd cydrannau mewn cyfres yn adio i foltedd ar draws y batri </t>
+  </si>
+  <si>
+    <t>(a) Cylched cyfres neu paralel?&lt;br&gt;&lt;br&gt;(b) Sut mae'r cerrynt drwy $A{_1}$ yn cymharu gyda $A_{2}$?</t>
+  </si>
+  <si>
+    <t>cylched_cyfres.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(a) cylched cyfres&lt;br&gt;&lt;br&gt; (b) mae cerrynt  $A_{1}$ yr  un peth </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>â</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> cerrynt $A_{2}$</t>
+    </r>
+  </si>
+  <si>
+    <t>lamp</t>
+  </si>
+  <si>
+    <t>symbol_lamp.png</t>
+  </si>
+  <si>
+    <t>LDR / GGD</t>
+  </si>
+  <si>
+    <t>symbol_LDR.png</t>
+  </si>
+  <si>
+    <t>cyflenwad pŵer</t>
+  </si>
+  <si>
+    <t>deuod</t>
+  </si>
+  <si>
+    <t>ffiws</t>
+  </si>
+  <si>
+    <t>thermistor</t>
+  </si>
+  <si>
+    <t>LED / DAG</t>
+  </si>
+  <si>
+    <t>symbol_LED.png</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Beth yw uned pŵer?</t>
+  </si>
+  <si>
+    <t>Pa ddyfais sy'n mesur cerrynt?</t>
+  </si>
+  <si>
+    <t>Pa ddyfais sy'n mesur foltedd?</t>
+  </si>
+  <si>
+    <t>Os yw gwrthyddion yn cael ychwanegu mewn &lt;b&gt;paralel&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
+  </si>
+  <si>
+    <t>Os yw gwrthyddion yn cael ychwanegu mewn &lt;b&gt;cyfres&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
+  </si>
+  <si>
+    <t>cynyddu</t>
+  </si>
+  <si>
+    <t>lleihau</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -337,6 +493,32 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -346,7 +528,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -361,11 +543,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -380,6 +599,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,6 +832,277 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1E61D9-C9D1-4E40-91DC-276BFC771A6A}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="676" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B719EFD-5DA2-4322-8FBD-8843A66FD33C}"/>
+  <xr:revisionPtr revIDLastSave="693" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1CEED58-DA39-4728-BFEE-57993ABB306C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="123">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -341,9 +342,6 @@
     <t xml:space="preserve">(a) Beth yw'r foltedd ar draws lamp $L_{2}$ a beth yw'r rheol?&lt;br&gt;&lt;br&gt; (b) Beth yw'r foltedd ar draws lamp $L_{4}$ a beth yw'r rheol? </t>
   </si>
   <si>
-    <t xml:space="preserve">(a) 8 V  - cydrannau mewn paralel gyda'r un foltedd &lt;br&gt;&lt;br&gt; (b) 9 V - foltedd cydrannau mewn cyfres yn adio i foltedd ar draws y batri </t>
-  </si>
-  <si>
     <t>(a) Cylched cyfres neu paralel?&lt;br&gt;&lt;br&gt;(b) Sut mae'r cerrynt drwy $A{_1}$ yn cymharu gyda $A_{2}$?</t>
   </si>
   <si>
@@ -415,16 +413,37 @@
     <t>Pa ddyfais sy'n mesur foltedd?</t>
   </si>
   <si>
-    <t>Os yw gwrthyddion yn cael ychwanegu mewn &lt;b&gt;paralel&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
-  </si>
-  <si>
-    <t>Os yw gwrthyddion yn cael ychwanegu mewn &lt;b&gt;cyfres&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
-  </si>
-  <si>
     <t>cynyddu</t>
   </si>
   <si>
     <t>lleihau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) 6 V  - cydrannau mewn paralel gyda'r un foltedd &lt;br&gt;&lt;br&gt; (b) 9 V - foltedd cydrannau mewn cyfres yn adio i foltedd ar draws y batri </t>
+  </si>
+  <si>
+    <t>symbol_cyflenwad_pwer.png</t>
+  </si>
+  <si>
+    <t>symbol_thermistor.png</t>
+  </si>
+  <si>
+    <t>symbol_ffiws.png</t>
+  </si>
+  <si>
+    <t>symbol_deuod.png</t>
+  </si>
+  <si>
+    <t>swits</t>
+  </si>
+  <si>
+    <t>symbol_swits.png</t>
+  </si>
+  <si>
+    <t>Os yw gwrthyddion yn cael eu ychwanegu mewn &lt;b&gt;paralel&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
+  </si>
+  <si>
+    <t>Os yw gwrthyddion yn cael eu ychwanegu mewn &lt;b&gt;cyfres&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
   </si>
 </sst>
 </file>
@@ -584,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -607,13 +626,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -832,7 +848,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.54296875" customWidth="1"/>
@@ -884,65 +900,69 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>83</v>
+      <c r="B6" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>84</v>
+      <c r="B7" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="1"/>
+      <c r="B10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -950,10 +970,10 @@
         <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -962,9 +982,11 @@
         <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -972,124 +994,139 @@
         <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
-        <v>88</v>
+      <c r="A21" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>91</v>
+      <c r="A22" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
-        <v>94</v>
+      <c r="A23" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>97</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="693" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1CEED58-DA39-4728-BFEE-57993ABB306C}"/>
+  <xr:revisionPtr revIDLastSave="842" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FC20DFE-72C4-4F54-A56F-50266FD8DF40}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
-    <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId2"/>
+    <sheet name="3.2 Cynhyrchu Trydan" sheetId="3" r:id="rId2"/>
+    <sheet name="3.3 Defnyddio Egni" sheetId="4" r:id="rId3"/>
+    <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="183">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -444,6 +445,186 @@
   </si>
   <si>
     <t>Os yw gwrthyddion yn cael eu ychwanegu mewn &lt;b&gt;cyfres&lt;/b&gt; mae cyfanswm gwrthiant y gylched yn (&lt;b&gt;lleihau/aros yr un peth/cynyddu&lt;/b&gt;)?</t>
+  </si>
+  <si>
+    <t>Sut mae gorsaf bŵer tanwydd ffosil yn generadu trydan?</t>
+  </si>
+  <si>
+    <t>Mae'r tanwydd yn cael ei losgi yn y boeler/ffwrnais er mwyn gwresogi dŵr. &lt;br&gt;&lt;br&gt; Mae'r &lt;b&gt;ager (steam)&lt;/b&gt;yn &lt;b&gt;troi tyrbin&lt;/b&gt;. &lt;br&gt;&lt;br&gt; Mae'r tyrbin yn &lt;b&gt;troi generadur&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Beth yw ffynhonnell egni &lt;b&gt;adnewyddadwy&lt;/b&gt;?</t>
+  </si>
+  <si>
+    <t>Ffynhonell egni sydd ddim yn rhedeg allan</t>
+  </si>
+  <si>
+    <t>Rhestrwch ffynonellau egni adnewyddadwy</t>
+  </si>
+  <si>
+    <t>gwynt&lt;br&gt;solar&lt;br&gt;trydan dŵr&lt;br&gt;pŵer llanw&lt;br&gt;pŵer tonnau&lt;br&gt;biomas</t>
+  </si>
+  <si>
+    <t>Beth yw ffynhonnell egni &lt;b&gt;anadnewyddadwy&lt;/b&gt;?</t>
+  </si>
+  <si>
+    <t>Ffynhonell egni sydd yn rhedeg allan</t>
+  </si>
+  <si>
+    <t>Rhestrwch ffynonellau egni anadnewyddadwy</t>
+  </si>
+  <si>
+    <t>glo&lt;br&gt;olew&lt;br&gt;nwy&lt;br&gt;niwclear</t>
+  </si>
+  <si>
+    <t>Pa nwy sy'n achosi glaw asid?</t>
+  </si>
+  <si>
+    <t>sylffwr deuocsid</t>
+  </si>
+  <si>
+    <t>Pa nwy sy'n cyfrannu fwyaf at gynhesu byd eang?</t>
+  </si>
+  <si>
+    <t>carbon deuocsid</t>
+  </si>
+  <si>
+    <t>Beth yw manteision gwynt,solar,pŵer tonnau,pŵer llanw?</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;br&gt;Adnewyddadwy&lt;br&gt;&lt;br&gt;Ddim yn allyrru $CO_{2}$ &lt;br&gt;&lt;br&gt;Ddim yn allyrru $SO_{2}$</t>
+  </si>
+  <si>
+    <t>Beth yw anfanteision gwynt,solar,pŵer tonnau?</t>
+  </si>
+  <si>
+    <t>Annibynawy</t>
+  </si>
+  <si>
+    <t>Beth yw mantais gorsaf bŵer niwclear?</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;br&gt;Dibynadwy&lt;br&gt;&lt;br&gt;Ddim yn allyrru $CO_{2}$ &lt;br&gt;&lt;br&gt;Cynhyrchu swm mawr o drydan</t>
+  </si>
+  <si>
+    <t>Beth yw anfantais gorsaf bŵer niwclear?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anadnewyddady&lt;br&gt;&lt;br&gt; Drud i'w gomisiynu (adeiladu) a datgomisiynu (cau lawr)&lt;br&gt;&lt;br&gt;Cynhyrchu gwastraff ymbelydrol peryglus </t>
+  </si>
+  <si>
+    <t>Beth yw newidydd codi?</t>
+  </si>
+  <si>
+    <t>Beth yw newidydd gostwng?</t>
+  </si>
+  <si>
+    <t>Newidydd sy'n cynyddu'r foltedd</t>
+  </si>
+  <si>
+    <t>Newidydd sy'n gostwng y foltedd</t>
+  </si>
+  <si>
+    <t>Beth yw'r Grid Cenedlaethol?</t>
+  </si>
+  <si>
+    <t>Rhwydwaith o geblau sy'n cysylltu bob gorsaf bŵer gyda phob defnyddiwr yn y wlad</t>
+  </si>
+  <si>
+    <t>Beth yw mantais ffynhonnell egni biomas?</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;br&gt;Adnewyddadwy&lt;br&gt;&lt;br&gt;Dibynadwy&lt;br&gt;&lt;br&gt;carbon niwtral</t>
+  </si>
+  <si>
+    <t>Beth yw anfantais ffynhonnell egni biomas?</t>
+  </si>
+  <si>
+    <t>Angen llawer o dir i dyfu coed/planhigion</t>
+  </si>
+  <si>
+    <t>Cynyddu'r foltedd er mwyn lleihau'r cerrynt ac felly colli llai o egni gwres yn y ceblau. Mae hyn yn cynyddu effeithlonrwydd y grid.</t>
+  </si>
+  <si>
+    <t>Eglurach pam bod angen &lt;b&gt;newidyddion codi&lt;/b&gt; yn y Grid Cenedlaethol?</t>
+  </si>
+  <si>
+    <t>Eglurach pam bod angen &lt;b&gt;newidyddion gostwng&lt;/b&gt; yn y Grid Cenedlaethol?</t>
+  </si>
+  <si>
+    <t>Gostwng y foltedd i lefel mwy diogel</t>
+  </si>
+  <si>
+    <t>Pelydriad</t>
+  </si>
+  <si>
+    <t>pelydriad.png</t>
+  </si>
+  <si>
+    <t>Dargludiad</t>
+  </si>
+  <si>
+    <t>dargludiad.png</t>
+  </si>
+  <si>
+    <t>Darfudiad</t>
+  </si>
+  <si>
+    <t>darfudiad.png</t>
+  </si>
+  <si>
+    <t>Beth yw unedau dwysedd?</t>
+  </si>
+  <si>
+    <t>$g/cm^{3}$ neu $kg/m_{3}$</t>
+  </si>
+  <si>
+    <t>Beth yw'r 3 dull mae gwres yn cael ei drosglwyddo o un lle i'r llall?</t>
+  </si>
+  <si>
+    <t>dargludiad, darfudiad, pelydriad</t>
+  </si>
+  <si>
+    <t>Beth yw'r dull o drosglwyddo gwres sydd yn y diagram?</t>
+  </si>
+  <si>
+    <t>ynysu_ty.png</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae gwydr ffibr/ewyn yn lleihau'r gwres sy'n cael ei golli drwy wal y tŷ</t>
+  </si>
+  <si>
+    <t>Mae gwydr ffibr/ewyn yn llawn swigod aer.&lt;br&gt;&lt;br&gt; Mae aer yn ynysydd da felly'n lleihau dargludiad.&lt;br&gt;&lt;br&gt; Ni all y swigod aer symud felly mae'n lleihau darfudiad.</t>
+  </si>
+  <si>
+    <t>Mae'r haen sgleiniog yn &lt;b&gt;adlewyrchu&lt;/b&gt; peldyriad gwres yn ôl i mewn i't tŷ.</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae'r haen &lt;b&gt;allanol&lt;/b&gt; sgleiniog ar y gwydr ffibr yn lleihau'r gwres sy'n cael ei golli drwy wal y tŷ.</t>
+  </si>
+  <si>
+    <t>Eglurwch sut mae'r haen &lt;b&gt;fewnol&lt;/b&gt; sgleiniog ar y gwydr ffibr yn lleihau'r gwres sy'n cael ei golli drwy wal y tŷ.</t>
+  </si>
+  <si>
+    <t>Mae arwyneb sgleiniog yn wael am &lt;b&gt;allyrru&lt;/b&gt; peldyriad gwres/isgoch felly mae llai o wres yn cael ei golli tuag allan.</t>
+  </si>
+  <si>
+    <t>Sut mae cyfrifo amser talu'n ôl?</t>
+  </si>
+  <si>
+    <t>$amser talu'n ôl  = \frac{cost gosod }{arbedion bob blwyddyn}$</t>
+  </si>
+  <si>
+    <t>Eglurwch yn nhermau &lt;b&gt;gronynnau&lt;/b&gt; sut mae egni gwres yn cael ei &lt;b&gt;ddargludo&lt;/b&gt; drwy rhoden fetel.</t>
+  </si>
+  <si>
+    <t>Mae atomau/ionau y pen sy'n cael ei wresogi yn dirgrynu’n gyflymach, yn gwrthdaro â’u cymdogion ac yn pasio'r egni ymlaen. &lt;br&gt;&lt;br&gt; Mae electronau rhydd yn symud drwy’r rhoden ac yn trosglwyddo’u hegni i'r atomau/ionau.</t>
+  </si>
+  <si>
+    <t>Eglurwch yn nhermau &lt;b&gt;gronynnau&lt;/b&gt; sut mae egni gwres yn cael ei &lt;b&gt;ddarfudo&lt;/b&gt; drwy hylif fel dŵr.</t>
+  </si>
+  <si>
+    <t>Mae gronynnau'r dŵr sy'n cael ei wresogi yn symud yn bellach oddi wrth ei gilydd. &lt;br&gt;&lt;br&gt; Mae'r dŵr poeth yn llai dwys felly yn codi.</t>
   </si>
 </sst>
 </file>
@@ -849,13 +1030,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,7 +1050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -879,7 +1060,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>74</v>
       </c>
@@ -889,7 +1070,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
@@ -898,7 +1079,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>109</v>
       </c>
@@ -907,7 +1088,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
@@ -919,7 +1100,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
@@ -930,7 +1111,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
@@ -941,7 +1122,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
@@ -953,7 +1134,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
@@ -965,7 +1146,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -977,7 +1158,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -989,7 +1170,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -1001,7 +1182,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
@@ -1012,7 +1193,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>82</v>
       </c>
@@ -1023,7 +1204,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>111</v>
       </c>
@@ -1032,7 +1213,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>110</v>
       </c>
@@ -1041,7 +1222,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
@@ -1052,7 +1233,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>85</v>
       </c>
@@ -1063,7 +1244,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>88</v>
       </c>
@@ -1075,7 +1256,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -1087,7 +1268,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>94</v>
       </c>
@@ -1099,7 +1280,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>95</v>
       </c>
@@ -1111,7 +1292,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>121</v>
       </c>
@@ -1121,7 +1302,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
@@ -1136,18 +1317,572 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE5441B-16C1-49EE-A8CF-229D09DD12A3}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="13"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="13"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="14"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="4"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="4"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="4"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="4"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7EC73C-7161-4F15-A4AA-BD16399A2341}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="15"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="15"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="13"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="13"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="13"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="13"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="13"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="14"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="14"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="4"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="4"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="4"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="4"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1E61D9-C9D1-4E40-91DC-276BFC771A6A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1171,7 +1906,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,7 +1916,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1193,7 +1928,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,7 +1940,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,7 +1949,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -1226,7 +1961,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -1238,7 +1973,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1247,7 +1982,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1256,7 +1991,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -1268,7 +2003,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -1280,7 +2015,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1290,7 +2025,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1300,7 +2035,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -1310,7 +2045,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -1320,7 +2055,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -1328,7 +2063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1336,7 +2071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,7 +2079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1352,7 +2087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -1360,7 +2095,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -1368,7 +2103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -1378,7 +2113,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>69</v>
       </c>
@@ -1388,7 +2123,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -1398,7 +2133,7 @@
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
@@ -1408,7 +2143,7 @@
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -1418,7 +2153,7 @@
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>56</v>
       </c>
@@ -1428,7 +2163,7 @@
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>57</v>
       </c>
@@ -1438,7 +2173,7 @@
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -1448,7 +2183,7 @@
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
@@ -1458,7 +2193,7 @@
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
@@ -1467,7 +2202,7 @@
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>70</v>
       </c>
@@ -1475,39 +2210,39 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="842" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FC20DFE-72C4-4F54-A56F-50266FD8DF40}"/>
+  <xr:revisionPtr revIDLastSave="846" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693F271B-52C7-4817-AA81-D0936796E30B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -456,9 +456,6 @@
     <t>Beth yw ffynhonnell egni &lt;b&gt;adnewyddadwy&lt;/b&gt;?</t>
   </si>
   <si>
-    <t>Ffynhonell egni sydd ddim yn rhedeg allan</t>
-  </si>
-  <si>
     <t>Rhestrwch ffynonellau egni adnewyddadwy</t>
   </si>
   <si>
@@ -468,9 +465,6 @@
     <t>Beth yw ffynhonnell egni &lt;b&gt;anadnewyddadwy&lt;/b&gt;?</t>
   </si>
   <si>
-    <t>Ffynhonell egni sydd yn rhedeg allan</t>
-  </si>
-  <si>
     <t>Rhestrwch ffynonellau egni anadnewyddadwy</t>
   </si>
   <si>
@@ -498,9 +492,6 @@
     <t>Beth yw anfanteision gwynt,solar,pŵer tonnau?</t>
   </si>
   <si>
-    <t>Annibynawy</t>
-  </si>
-  <si>
     <t>Beth yw mantais gorsaf bŵer niwclear?</t>
   </si>
   <si>
@@ -612,9 +603,6 @@
     <t>Sut mae cyfrifo amser talu'n ôl?</t>
   </si>
   <si>
-    <t>$amser talu'n ôl  = \frac{cost gosod }{arbedion bob blwyddyn}$</t>
-  </si>
-  <si>
     <t>Eglurwch yn nhermau &lt;b&gt;gronynnau&lt;/b&gt; sut mae egni gwres yn cael ei &lt;b&gt;ddargludo&lt;/b&gt; drwy rhoden fetel.</t>
   </si>
   <si>
@@ -625,6 +613,18 @@
   </si>
   <si>
     <t>Mae gronynnau'r dŵr sy'n cael ei wresogi yn symud yn bellach oddi wrth ei gilydd. &lt;br&gt;&lt;br&gt; Mae'r dŵr poeth yn llai dwys felly yn codi.</t>
+  </si>
+  <si>
+    <t>Ffynhonnell egni sydd ddim yn rhedeg allan</t>
+  </si>
+  <si>
+    <t>Ffynhonnell egni sydd yn rhedeg allan</t>
+  </si>
+  <si>
+    <t>Annibynadwy</t>
+  </si>
+  <si>
+    <t>amser talu'n ôl  = $\frac{\text{cost gosod} }{\text{arbedion bob blwyddyn?}$</t>
   </si>
 </sst>
 </file>
@@ -1030,13 +1030,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -1060,7 +1060,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>74</v>
       </c>
@@ -1070,7 +1070,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>109</v>
       </c>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>82</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>111</v>
       </c>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>110</v>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>85</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>88</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>94</v>
       </c>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>95</v>
       </c>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>121</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
@@ -1322,13 +1322,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1342,47 +1342,47 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
@@ -1392,191 +1392,191 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B9" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>139</v>
-      </c>
       <c r="B10" s="15" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="9"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14"/>
       <c r="B28" s="9"/>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11"/>
       <c r="B31" s="9"/>
     </row>
@@ -1592,13 +1592,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1612,255 +1612,255 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="B9" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="12"/>
       <c r="B14" s="15"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12"/>
       <c r="B15" s="15"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13"/>
       <c r="B18" s="15"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="6"/>
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="6"/>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="9"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="B32" s="9"/>
       <c r="C32" s="4"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
     </row>
@@ -1876,13 +1876,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1906,7 +1906,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1916,7 +1916,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -2045,7 +2045,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2055,7 +2055,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>69</v>
       </c>
@@ -2123,7 +2123,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
@@ -2143,7 +2143,7 @@
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>56</v>
       </c>
@@ -2163,7 +2163,7 @@
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>57</v>
       </c>
@@ -2173,7 +2173,7 @@
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -2183,7 +2183,7 @@
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
@@ -2193,7 +2193,7 @@
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>70</v>
       </c>
@@ -2210,39 +2210,39 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="846" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693F271B-52C7-4817-AA81-D0936796E30B}"/>
+  <xr:revisionPtr revIDLastSave="847" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C604DA3B-3FDD-4B09-BC30-B857AADAA311}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,7 +624,7 @@
     <t>Annibynadwy</t>
   </si>
   <si>
-    <t>amser talu'n ôl  = $\frac{\text{cost gosod} }{\text{arbedion bob blwyddyn?}$</t>
+    <t>amser talu'n ôl  = $\frac{cost~gosod}{arbedion~bob~blwyddyn?}$</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="847" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C604DA3B-3FDD-4B09-BC30-B857AADAA311}"/>
+  <xr:revisionPtr revIDLastSave="848" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90E8CD83-7DB7-454F-A136-C0E71CD7D44D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -567,9 +567,6 @@
     <t>Beth yw unedau dwysedd?</t>
   </si>
   <si>
-    <t>$g/cm^{3}$ neu $kg/m_{3}$</t>
-  </si>
-  <si>
     <t>Beth yw'r 3 dull mae gwres yn cael ei drosglwyddo o un lle i'r llall?</t>
   </si>
   <si>
@@ -625,6 +622,9 @@
   </si>
   <si>
     <t>amser talu'n ôl  = $\frac{cost~gosod}{arbedion~bob~blwyddyn?}$</t>
+  </si>
+  <si>
+    <t>$g/cm^{3}$ neu $kg/m^{3}$</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1347,7 @@
         <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1367,7 +1367,7 @@
         <v>128</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1425,7 +1425,7 @@
         <v>137</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
@@ -1614,17 +1614,17 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>156</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>158</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>160</v>
@@ -1660,46 +1660,46 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
@@ -1709,27 +1709,27 @@
         <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90E8CD83-7DB7-454F-A136-C0E71CD7D44D}"/>
+  <xr:revisionPtr revIDLastSave="903" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3988B88-4225-4090-B0F3-0EC5FBEB58BD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
     <sheet name="3.2 Cynhyrchu Trydan" sheetId="3" r:id="rId2"/>
     <sheet name="3.3 Defnyddio Egni" sheetId="4" r:id="rId3"/>
-    <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId4"/>
+    <sheet name="3.4 Trydan Domestig" sheetId="5" r:id="rId4"/>
+    <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="212">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -621,10 +622,97 @@
     <t>Annibynadwy</t>
   </si>
   <si>
-    <t>amser talu'n ôl  = $\frac{cost~gosod}{arbedion~bob~blwyddyn?}$</t>
-  </si>
-  <si>
     <t>$g/cm^{3}$ neu $kg/m^{3}$</t>
+  </si>
+  <si>
+    <t>amser talu'n ôl  = $\frac{cost~gosod}{arbedion~bob~blwyddyn}$</t>
+  </si>
+  <si>
+    <t>Beth yw'r unedau mae'r cwmni trydan yn ddefnyddio i fesur faint o egni trydanol rydych yn ddefnyddio?</t>
+  </si>
+  <si>
+    <t>kWawr</t>
+  </si>
+  <si>
+    <t>Sut mae ffiws yn gweithio?</t>
+  </si>
+  <si>
+    <t>Os yw'r cerrynt yn rhy uchel mae'r ffiws yn chwythu ac yn torri'r gylched</t>
+  </si>
+  <si>
+    <t>Sut mae torrwr cylched bach (mcb) yn gweithio?</t>
+  </si>
+  <si>
+    <t>Beth yw mainteision torrwr cylched bach (mcb) dros ffiws?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mae mcb yn gweithio'n gyflmach na ffiws. &lt;br&gt;&lt;br&gt; Gallwn ailosod mcb </t>
+  </si>
+  <si>
+    <t>Mae'n cymharu y cerrynt yn y wifren fyw a'r wifren niwtral. Os ydynt yn wahanol mae'r torri'r gylched yn gyflym iawn.</t>
+  </si>
+  <si>
+    <t>Ffiws&lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt; torrwr cylched bach</t>
+  </si>
+  <si>
+    <t>Pa ddyfeisiau sy'n stopio gwifrau rhag gorboethi?</t>
+  </si>
+  <si>
+    <t>Pa ddyfeisiau sy'n atal siocau trydan?</t>
+  </si>
+  <si>
+    <t>dyfais cerrynt gweddilliol (rcd) &lt;br&gt;&lt;br&gt; neu &lt;br&gt;&lt;br&gt; y wifren ddaearu</t>
+  </si>
+  <si>
+    <t>Sut mae torrwr cylched cerrynt gweddilliol (rccb neu rcd) yn gweithio?</t>
+  </si>
+  <si>
+    <t>$amser talu'n ôl = \frac{\text{cost gosod (£)} }{\text{arbedion bob blwyddyn (£) } }</t>
+  </si>
+  <si>
+    <t>Beth yw'r hafaliad i gyfrifo amser talu'n ôl?</t>
+  </si>
+  <si>
+    <t>Beth yw c.e.?</t>
+  </si>
+  <si>
+    <t>cerrynt eiledol - cerrynt sydd yn newid mewn maint a chyfeiriad</t>
+  </si>
+  <si>
+    <t>Beth yw c.u.?</t>
+  </si>
+  <si>
+    <t>cerrynt union - cerrynt ddim yn newid.</t>
+  </si>
+  <si>
+    <t>Beth yw swyddogaeth (pwrpas) y wifren fyw?</t>
+  </si>
+  <si>
+    <t>Beth yw swyddogaeth (pwrpas) y wifren niwtral?</t>
+  </si>
+  <si>
+    <t>Mae’r wifren fyw yn cludo cerrynt i ddyfais ar foltedd uchel</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas y wifren ddaearu?</t>
+  </si>
+  <si>
+    <t>darparu llwybr gwrthiant isel i gerrynt lifo i'r ddaear.</t>
+  </si>
+  <si>
+    <t>Mae'r wifren niwtral yn cwblhau'r gylched ac yn cludo cerrynt ar foltedd isel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa liw yw'r wifren fyw,niwtral a'r ddaear? </t>
+  </si>
+  <si>
+    <t>byw - brown &lt;br&gt;&lt;br&gt; niwtral - glas &lt;br&gt;&lt;br&gt; daear - gwyrdd a melyn</t>
+  </si>
+  <si>
+    <t>Beth yw manteision prif gylched cylch?</t>
+  </si>
+  <si>
+    <t>Dau lwybr i'r cerrynt lifo felly gallwch wneud y gwifrau'n deneuach a chael cerrynt is yn y ddwy ran &lt;br&gt;&lt;br&gt; gallu ychwanegu mwy o socedau yn unrhyw le ar y cylch a bydd yr un foltedd i bob un (240V).</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1787,7 @@
         <v>173</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
@@ -1709,7 +1797,7 @@
         <v>162</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1871,6 +1959,306 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C4504A-DA83-4DBE-B0D5-8E835209B134}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="12"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="13"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="13"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="13"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="4"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="4"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="4"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="11"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="4"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11"/>
+      <c r="B38" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1E61D9-C9D1-4E40-91DC-276BFC771A6A}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="903" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3988B88-4225-4090-B0F3-0EC5FBEB58BD}"/>
+  <xr:revisionPtr revIDLastSave="905" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C4F1135-3E21-48C8-A3C0-0B30C8BB03FA}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="213">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -667,9 +667,6 @@
     <t>Sut mae torrwr cylched cerrynt gweddilliol (rccb neu rcd) yn gweithio?</t>
   </si>
   <si>
-    <t>$amser talu'n ôl = \frac{\text{cost gosod (£)} }{\text{arbedion bob blwyddyn (£) } }</t>
-  </si>
-  <si>
     <t>Beth yw'r hafaliad i gyfrifo amser talu'n ôl?</t>
   </si>
   <si>
@@ -713,6 +710,12 @@
   </si>
   <si>
     <t>Dau lwybr i'r cerrynt lifo felly gallwch wneud y gwifrau'n deneuach a chael cerrynt is yn y ddwy ran &lt;br&gt;&lt;br&gt; gallu ychwanegu mwy o socedau yn unrhyw le ar y cylch a bydd yr un foltedd i bob un (240V).</t>
+  </si>
+  <si>
+    <t>Os yw'r cerrynt yn rhy uchel mae'r mcb yn torri'r gylched</t>
+  </si>
+  <si>
+    <t>$amser talu'n ôl = \frac{\text{cost gosod (£)} }{\text{arbedion bob blwyddyn (£) } }$</t>
   </si>
 </sst>
 </file>
@@ -1996,20 +1999,20 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -2029,7 +2032,7 @@
         <v>187</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
@@ -2076,59 +2079,59 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>208</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>209</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>210</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>211</v>
       </c>
       <c r="D16" s="1"/>
     </row>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="905" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C4F1135-3E21-48C8-A3C0-0B30C8BB03FA}"/>
+  <xr:revisionPtr revIDLastSave="906" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC128B7E-BD4E-48B4-89B6-094D7B501A79}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -715,7 +715,7 @@
     <t>Os yw'r cerrynt yn rhy uchel mae'r mcb yn torri'r gylched</t>
   </si>
   <si>
-    <t>$amser talu'n ôl = \frac{\text{cost gosod (£)} }{\text{arbedion bob blwyddyn (£) } }$</t>
+    <t>amser talu'n ôl = $\frac{cost gosod (£)}{arbedion bob blwyddyn (£)  }$</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="906" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC128B7E-BD4E-48B4-89B6-094D7B501A79}"/>
+  <xr:revisionPtr revIDLastSave="907" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B2D804-C4B5-4F26-9F9B-8504166810E4}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -715,7 +715,7 @@
     <t>Os yw'r cerrynt yn rhy uchel mae'r mcb yn torri'r gylched</t>
   </si>
   <si>
-    <t>amser talu'n ôl = $\frac{cost gosod (£)}{arbedion bob blwyddyn (£)  }$</t>
+    <t>amser talu'n ôl = $\frac{\text{cost gosod (£)}}{arbedion bob blwyddyn (£)  }$</t>
   </si>
 </sst>
 </file>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="907" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B2D804-C4B5-4F26-9F9B-8504166810E4}"/>
+  <xr:revisionPtr revIDLastSave="953" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F37FFEA-183B-41DD-9D5A-D5A5ED504B66}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="3.3 Defnyddio Egni" sheetId="4" r:id="rId3"/>
     <sheet name="3.4 Trydan Domestig" sheetId="5" r:id="rId4"/>
     <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId5"/>
+    <sheet name="1.6 Adlewyrchiad mewnol cyflawn" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="232">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -717,12 +718,80 @@
   <si>
     <t>amser talu'n ôl = $\frac{\text{cost gosod (£)}}{arbedion bob blwyddyn (£)  }$</t>
   </si>
+  <si>
+    <t>Beth yw'r ddau amod sydd eu hangen ar gyfer adlewyrchiad mewnol cyflawn?</t>
+  </si>
+  <si>
+    <t>Rhaid i'r golau deithio o ddefnydd mwy dwys tuag at defnydd llai dwys (e.e. gwydr i aer). &lt;br&gt;&lt;br&gt; Rhaid i'r ongl drawol fod yn fwy na'r ongl gritigol.</t>
+  </si>
+  <si>
+    <t>Nodwch ddefnydd o adlewyrchiad mewnol cyflawn</t>
+  </si>
+  <si>
+    <t>Ffibrau optegol &lt;br&gt;&lt;br&gt; Endosgop &lt;br&gt;&lt;br&gt; Perisgop&lt;br&gt;&lt;br&gt; Llygaid cath</t>
+  </si>
+  <si>
+    <t>Pa ddiagram sy'n dangos plygiant golau?</t>
+  </si>
+  <si>
+    <t>adlewyrchiad_mewnol_cyflawn.png</t>
+  </si>
+  <si>
+    <t>A neu B</t>
+  </si>
+  <si>
+    <t>Ym mha ddiagram mae'r ongl drawol(i) yn hafal i'r ongl gritigol?</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Pa ddiagram sy'n dangos adlewyrchiad mewnol cyflawn?</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Beth yw gwerth yr ongl plygiant pan mae'r ongl drawol(i) yn hafal i'r ongl gritigol?</t>
+  </si>
+  <si>
+    <r>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>˚</t>
+    </r>
+  </si>
+  <si>
+    <t>Beth yw manteision trawsyrru gwybodaeth drwy ffibrau optegol o gymharu â lloerenni?</t>
+  </si>
+  <si>
+    <t>Gallu trawsyrru fata ar gyfraddau (rate) uwch. &lt;br&gt;&lt;br&gt;Mwy dibynadwy&lt;br&gt;&lt;br&gt; Oediad amser byrrach&lt;br&gt;&lt;br&gt; Costau llai &lt;br&gt;&lt;br&gt; Diogelwch - ni ellir rhyng-gipio signalau.&lt;br&gt;&lt;br&gt; Llai o ymyrriant (e.e. gan y tywydd)</t>
+  </si>
+  <si>
+    <t>Rhowch anfantais o ddefnyddio sgan CT i gael gwybodaeth feddygol o gymharu â defnyddio endosgop.</t>
+  </si>
+  <si>
+    <t>Mae sganiau CT yn defnyddio pelydrau-X sydd yn ioneiddio celloedd ac yn gallu achosi canser.</t>
+  </si>
+  <si>
+    <t>Rhowch fantais o ddefnyddio sgan CT i gael gwybodaeth feddygol o gymharu â defnyddio endosgop.</t>
+  </si>
+  <si>
+    <t>Maent yn rhoi darlun mwy cyffredinol, mae endosgop yn rhoi darlun ar rannau penodol.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -810,6 +879,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -875,7 +951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -902,6 +978,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2641,4 +2718,117 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33D1AC1-9022-47FD-BF0B-FE4924AEB9BF}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="953" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F37FFEA-183B-41DD-9D5A-D5A5ED504B66}"/>
+  <xr:revisionPtr revIDLastSave="954" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F151413-4C76-4C3A-96B5-3D5674664508}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,9 +772,6 @@
     <t>Beth yw manteision trawsyrru gwybodaeth drwy ffibrau optegol o gymharu â lloerenni?</t>
   </si>
   <si>
-    <t>Gallu trawsyrru fata ar gyfraddau (rate) uwch. &lt;br&gt;&lt;br&gt;Mwy dibynadwy&lt;br&gt;&lt;br&gt; Oediad amser byrrach&lt;br&gt;&lt;br&gt; Costau llai &lt;br&gt;&lt;br&gt; Diogelwch - ni ellir rhyng-gipio signalau.&lt;br&gt;&lt;br&gt; Llai o ymyrriant (e.e. gan y tywydd)</t>
-  </si>
-  <si>
     <t>Rhowch anfantais o ddefnyddio sgan CT i gael gwybodaeth feddygol o gymharu â defnyddio endosgop.</t>
   </si>
   <si>
@@ -785,6 +782,9 @@
   </si>
   <si>
     <t>Maent yn rhoi darlun mwy cyffredinol, mae endosgop yn rhoi darlun ar rannau penodol.</t>
+  </si>
+  <si>
+    <t>Gallu trawsyrru data ar gyfraddau (rate) uwch. &lt;br&gt;&lt;br&gt;Mwy dibynadwy&lt;br&gt;&lt;br&gt; Oediad amser byrrach&lt;br&gt;&lt;br&gt; Costau llai &lt;br&gt;&lt;br&gt; Diogelwch - ni ellir rhyng-gipio signalau.&lt;br&gt;&lt;br&gt; Llai o ymyrriant (e.e. gan y tywydd)</t>
   </si>
 </sst>
 </file>
@@ -2805,23 +2805,23 @@
         <v>226</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="954" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F151413-4C76-4C3A-96B5-3D5674664508}"/>
+  <xr:revisionPtr revIDLastSave="956" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC7EB82-D0B2-41B7-B16F-81E833A9C45D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-720" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="234">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -785,6 +785,12 @@
   </si>
   <si>
     <t>Gallu trawsyrru data ar gyfraddau (rate) uwch. &lt;br&gt;&lt;br&gt;Mwy dibynadwy&lt;br&gt;&lt;br&gt; Oediad amser byrrach&lt;br&gt;&lt;br&gt; Costau llai &lt;br&gt;&lt;br&gt; Diogelwch - ni ellir rhyng-gipio signalau.&lt;br&gt;&lt;br&gt; Llai o ymyrriant (e.e. gan y tywydd)</t>
+  </si>
+  <si>
+    <t>Beth yw pwrpas gwrthydd newidiol?</t>
+  </si>
+  <si>
+    <t>Mae'n newid y gwrthiant ac felly y cerrynt yn y gylched.</t>
   </si>
 </sst>
 </file>
@@ -951,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -979,6 +985,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1197,14 +1206,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1218,7 +1227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -1228,7 +1237,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>74</v>
       </c>
@@ -1238,7 +1247,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
@@ -1247,7 +1256,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>109</v>
       </c>
@@ -1256,7 +1265,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
@@ -1268,7 +1277,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
@@ -1279,7 +1288,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
@@ -1290,7 +1299,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
@@ -1302,7 +1311,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
@@ -1314,7 +1323,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -1326,7 +1335,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -1338,7 +1347,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -1350,7 +1359,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
@@ -1361,7 +1370,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>82</v>
       </c>
@@ -1372,7 +1381,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>111</v>
       </c>
@@ -1381,7 +1390,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>110</v>
       </c>
@@ -1390,7 +1399,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
@@ -1401,7 +1410,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>85</v>
       </c>
@@ -1412,7 +1421,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>88</v>
       </c>
@@ -1424,7 +1433,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -1436,7 +1445,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>94</v>
       </c>
@@ -1448,7 +1457,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>95</v>
       </c>
@@ -1460,7 +1469,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>121</v>
       </c>
@@ -1470,12 +1479,20 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1490,13 +1507,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
@@ -1520,7 +1537,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
@@ -1530,7 +1547,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
@@ -1540,7 +1557,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>129</v>
       </c>
@@ -1550,7 +1567,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
@@ -1560,7 +1577,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
@@ -1570,7 +1587,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>133</v>
       </c>
@@ -1579,7 +1596,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>135</v>
       </c>
@@ -1588,7 +1605,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
@@ -1598,7 +1615,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>138</v>
       </c>
@@ -1607,7 +1624,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>140</v>
       </c>
@@ -1616,7 +1633,7 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>148</v>
       </c>
@@ -1625,7 +1642,7 @@
       </c>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>150</v>
       </c>
@@ -1634,7 +1651,7 @@
       </c>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>142</v>
       </c>
@@ -1644,7 +1661,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>143</v>
       </c>
@@ -1654,7 +1671,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>146</v>
       </c>
@@ -1664,7 +1681,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>153</v>
       </c>
@@ -1674,7 +1691,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>154</v>
       </c>
@@ -1684,67 +1701,67 @@
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="9"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="9"/>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="9"/>
     </row>
@@ -1760,13 +1777,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1780,7 +1797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>163</v>
       </c>
@@ -1790,7 +1807,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>165</v>
       </c>
@@ -1802,7 +1819,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>165</v>
       </c>
@@ -1814,7 +1831,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>165</v>
       </c>
@@ -1826,7 +1843,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>167</v>
       </c>
@@ -1838,7 +1855,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>171</v>
       </c>
@@ -1850,7 +1867,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>170</v>
       </c>
@@ -1862,7 +1879,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>173</v>
       </c>
@@ -1872,7 +1889,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>162</v>
       </c>
@@ -1882,7 +1899,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>174</v>
       </c>
@@ -1892,7 +1909,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>176</v>
       </c>
@@ -1902,133 +1919,133 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="15"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="15"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="15"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="6"/>
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="6"/>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="9"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="9"/>
       <c r="C32" s="4"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
     </row>
@@ -2044,13 +2061,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2064,7 +2081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>183</v>
       </c>
@@ -2074,7 +2091,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>197</v>
       </c>
@@ -2084,7 +2101,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>199</v>
       </c>
@@ -2094,7 +2111,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>185</v>
       </c>
@@ -2104,7 +2121,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>187</v>
       </c>
@@ -2114,7 +2131,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>188</v>
       </c>
@@ -2124,7 +2141,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>195</v>
       </c>
@@ -2134,7 +2151,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>192</v>
       </c>
@@ -2144,7 +2161,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>193</v>
       </c>
@@ -2154,7 +2171,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>196</v>
       </c>
@@ -2164,7 +2181,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>201</v>
       </c>
@@ -2174,7 +2191,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -2184,7 +2201,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>204</v>
       </c>
@@ -2194,7 +2211,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>207</v>
       </c>
@@ -2203,7 +2220,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>209</v>
       </c>
@@ -2212,123 +2229,123 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="15"/>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="7"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="15"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="6"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="6"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
       <c r="C36" s="4"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="9"/>
       <c r="C37" s="4"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="9"/>
     </row>
@@ -2344,13 +2361,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2364,7 +2381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2374,7 +2391,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -2384,7 +2401,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2396,7 +2413,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2408,7 +2425,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2417,7 +2434,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -2429,7 +2446,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -2441,7 +2458,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -2450,7 +2467,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -2459,7 +2476,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2471,7 +2488,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -2483,7 +2500,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -2493,7 +2510,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2503,7 +2520,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -2513,7 +2530,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2523,7 +2540,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -2531,7 +2548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2539,7 +2556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2547,7 +2564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2555,7 +2572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2563,7 +2580,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -2571,7 +2588,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -2581,7 +2598,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>69</v>
       </c>
@@ -2591,7 +2608,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2601,7 +2618,7 @@
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
@@ -2611,7 +2628,7 @@
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -2621,7 +2638,7 @@
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>56</v>
       </c>
@@ -2631,7 +2648,7 @@
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>57</v>
       </c>
@@ -2641,7 +2658,7 @@
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -2651,7 +2668,7 @@
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
@@ -2661,7 +2678,7 @@
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
@@ -2670,7 +2687,7 @@
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>70</v>
       </c>
@@ -2678,39 +2695,39 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>
@@ -2723,13 +2740,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33D1AC1-9022-47FD-BF0B-FE4924AEB9BF}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2743,7 +2760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>213</v>
       </c>
@@ -2751,7 +2768,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>215</v>
       </c>
@@ -2759,7 +2776,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>217</v>
       </c>
@@ -2770,7 +2787,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -2781,7 +2798,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -2792,7 +2809,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>224</v>
       </c>
@@ -2800,7 +2817,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>226</v>
       </c>
@@ -2808,7 +2825,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>227</v>
       </c>
@@ -2816,7 +2833,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>229</v>
       </c>
@@ -2824,7 +2841,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" s="16"/>
     </row>
   </sheetData>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="956" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC7EB82-D0B2-41B7-B16F-81E833A9C45D}"/>
+  <xr:revisionPtr revIDLastSave="1006" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29CD53C3-0C27-4D25-B6F4-15240A76266A}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-720" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="3.4 Trydan Domestig" sheetId="5" r:id="rId4"/>
     <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId5"/>
     <sheet name="1.6 Adlewyrchiad mewnol cyflawn" sheetId="6" r:id="rId6"/>
+    <sheet name="1.7 Tonnau Seismig" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="265">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -791,6 +792,99 @@
   </si>
   <si>
     <t>Mae'n newid y gwrthiant ac felly y cerrynt yn y gylched.</t>
+  </si>
+  <si>
+    <t>Rhestrwch y tri math o donnau seismig</t>
+  </si>
+  <si>
+    <t>Tonnau P&lt;br&gt;&lt;br&gt; Tonnau S&lt;br&gt;&lt;br&gt; Tonnau arwyneb</t>
+  </si>
+  <si>
+    <t>Arhydol/hydredol</t>
+  </si>
+  <si>
+    <t>Pa fath o don yw Tonnau S?</t>
+  </si>
+  <si>
+    <t>Ardraws</t>
+  </si>
+  <si>
+    <t>Pa donnau yw'r mwyaf cyflym?</t>
+  </si>
+  <si>
+    <t>Tonnau P</t>
+  </si>
+  <si>
+    <t>Pa donnau yw'r mwyaf araf?</t>
+  </si>
+  <si>
+    <t>Tonnau arwyneb</t>
+  </si>
+  <si>
+    <t>Pa fath o don yw tonnau P?</t>
+  </si>
+  <si>
+    <t>Trwy beth mae tonnau P yn gallu teithio?</t>
+  </si>
+  <si>
+    <t>solid yn unig</t>
+  </si>
+  <si>
+    <t>craig solid a hylif</t>
+  </si>
+  <si>
+    <t>Trwy beth mae tonnau S yn gallu teithio?</t>
+  </si>
+  <si>
+    <t>Trwy beth mae tonnau arwyneb yn gallu teithio?</t>
+  </si>
+  <si>
+    <t>arwyneb y Ddaear yn unig</t>
+  </si>
+  <si>
+    <t>cramen denau solid&lt;br&gt;&lt;br&gt; mantell solid&lt;br&gt;&lt;br&gt; craidd hylifol</t>
+  </si>
+  <si>
+    <t>Adeiledd_y_Ddaear.png</t>
+  </si>
+  <si>
+    <t>Disgrifiwch model o adeiledd y Ddaear.</t>
+  </si>
+  <si>
+    <t>Pa fath o donnau sy'n cyrraedd C</t>
+  </si>
+  <si>
+    <t>Tonnau P ac S</t>
+  </si>
+  <si>
+    <t>Pa fath o donnau sy'n cyrraedd B</t>
+  </si>
+  <si>
+    <t>Tonnau P yn unig</t>
+  </si>
+  <si>
+    <t>Ardal_gysgodol_tonS.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni all y tonnau S deithio drwy craidd y Ddaear.&lt;br&gt;&lt;br&gt; Ni all tonnau S deithio drwy hylif felly mae'n rhaid bod y craidd yn hylif. </t>
+  </si>
+  <si>
+    <t>Eglurwch beth mae'r ardal gysgodol yn ddweud wrthon ni am adeiledd y Ddaear.</t>
+  </si>
+  <si>
+    <t>gorsafoedd_seismig.png</t>
+  </si>
+  <si>
+    <t>Pam bod tonnau P yn cyrraedd bob gorsaf o flaen tonnau S?</t>
+  </si>
+  <si>
+    <t>Mae tonnau P yn gyflymch na tonnau S</t>
+  </si>
+  <si>
+    <t>Pam bod y tonnau seismig yn cyrraedd gorsaf A cyn gorsaf B?</t>
+  </si>
+  <si>
+    <t>Mae gorsaf A yn agosach i'r daeargryn na gorsaf B.</t>
   </si>
 </sst>
 </file>
@@ -985,7 +1079,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1207,13 +1301,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1227,7 +1321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -1237,7 +1331,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>74</v>
       </c>
@@ -1247,7 +1341,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
@@ -1256,7 +1350,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>109</v>
       </c>
@@ -1265,7 +1359,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
@@ -1277,7 +1371,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
@@ -1288,7 +1382,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
@@ -1299,7 +1393,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
@@ -1311,7 +1405,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
@@ -1323,7 +1417,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -1335,7 +1429,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -1347,7 +1441,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -1359,7 +1453,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
@@ -1370,7 +1464,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>82</v>
       </c>
@@ -1381,7 +1475,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>111</v>
       </c>
@@ -1390,7 +1484,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>110</v>
       </c>
@@ -1399,7 +1493,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
@@ -1410,7 +1504,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>85</v>
       </c>
@@ -1421,7 +1515,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>88</v>
       </c>
@@ -1433,7 +1527,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -1445,7 +1539,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>94</v>
       </c>
@@ -1457,7 +1551,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>95</v>
       </c>
@@ -1469,7 +1563,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>121</v>
       </c>
@@ -1479,7 +1573,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
@@ -1487,7 +1581,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
         <v>232</v>
       </c>
@@ -1507,13 +1601,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
@@ -1537,7 +1631,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
@@ -1547,7 +1641,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
@@ -1557,7 +1651,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>129</v>
       </c>
@@ -1567,7 +1661,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
@@ -1577,7 +1671,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
@@ -1587,7 +1681,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>133</v>
       </c>
@@ -1596,7 +1690,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
         <v>135</v>
       </c>
@@ -1605,7 +1699,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
         <v>137</v>
       </c>
@@ -1615,7 +1709,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>138</v>
       </c>
@@ -1624,7 +1718,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>140</v>
       </c>
@@ -1633,7 +1727,7 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>148</v>
       </c>
@@ -1642,7 +1736,7 @@
       </c>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>150</v>
       </c>
@@ -1651,7 +1745,7 @@
       </c>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>142</v>
       </c>
@@ -1661,7 +1755,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>143</v>
       </c>
@@ -1671,7 +1765,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>146</v>
       </c>
@@ -1681,7 +1775,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>153</v>
       </c>
@@ -1691,7 +1785,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>154</v>
       </c>
@@ -1701,67 +1795,67 @@
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="9"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14"/>
       <c r="B28" s="9"/>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11"/>
       <c r="B31" s="9"/>
     </row>
@@ -1777,13 +1871,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1797,7 +1891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>163</v>
       </c>
@@ -1807,7 +1901,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>165</v>
       </c>
@@ -1819,7 +1913,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>165</v>
       </c>
@@ -1831,7 +1925,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>165</v>
       </c>
@@ -1843,7 +1937,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>167</v>
       </c>
@@ -1855,7 +1949,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>171</v>
       </c>
@@ -1867,7 +1961,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>170</v>
       </c>
@@ -1879,7 +1973,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>173</v>
       </c>
@@ -1889,7 +1983,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>162</v>
       </c>
@@ -1899,7 +1993,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>174</v>
       </c>
@@ -1909,7 +2003,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>176</v>
       </c>
@@ -1919,133 +2013,133 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="12"/>
       <c r="B14" s="15"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12"/>
       <c r="B15" s="15"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13"/>
       <c r="B18" s="15"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="6"/>
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="6"/>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="9"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11"/>
       <c r="B32" s="9"/>
       <c r="C32" s="4"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
     </row>
@@ -2061,13 +2155,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2081,7 +2175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>183</v>
       </c>
@@ -2091,7 +2185,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>197</v>
       </c>
@@ -2101,7 +2195,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>199</v>
       </c>
@@ -2111,7 +2205,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>185</v>
       </c>
@@ -2121,7 +2215,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>187</v>
       </c>
@@ -2131,7 +2225,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>188</v>
       </c>
@@ -2141,7 +2235,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>195</v>
       </c>
@@ -2151,7 +2245,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>192</v>
       </c>
@@ -2161,7 +2255,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>193</v>
       </c>
@@ -2171,7 +2265,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>196</v>
       </c>
@@ -2181,7 +2275,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>201</v>
       </c>
@@ -2191,7 +2285,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -2201,7 +2295,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>204</v>
       </c>
@@ -2211,7 +2305,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
         <v>207</v>
       </c>
@@ -2220,7 +2314,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
         <v>209</v>
       </c>
@@ -2229,123 +2323,123 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="12"/>
       <c r="B17" s="15"/>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
       <c r="B18" s="7"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13"/>
       <c r="B20" s="15"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="6"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="6"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
       <c r="C36" s="4"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11"/>
       <c r="B37" s="9"/>
       <c r="C37" s="4"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11"/>
       <c r="B38" s="9"/>
     </row>
@@ -2361,13 +2455,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="1" max="1" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2381,7 +2475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2391,7 +2485,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -2401,7 +2495,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2413,7 +2507,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2425,7 +2519,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2434,7 +2528,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -2446,7 +2540,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -2458,7 +2552,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -2467,7 +2561,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -2476,7 +2570,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2488,7 +2582,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -2500,7 +2594,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -2510,7 +2604,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2520,7 +2614,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -2530,7 +2624,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2540,7 +2634,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -2548,7 +2642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2556,7 +2650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2564,7 +2658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2572,7 +2666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2580,7 +2674,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -2588,7 +2682,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -2598,7 +2692,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>69</v>
       </c>
@@ -2608,7 +2702,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2618,7 +2712,7 @@
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
@@ -2628,7 +2722,7 @@
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -2638,7 +2732,7 @@
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>56</v>
       </c>
@@ -2648,7 +2742,7 @@
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>57</v>
       </c>
@@ -2658,7 +2752,7 @@
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -2668,7 +2762,7 @@
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
@@ -2678,7 +2772,7 @@
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
@@ -2687,7 +2781,7 @@
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>70</v>
       </c>
@@ -2695,39 +2789,39 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>
@@ -2740,13 +2834,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33D1AC1-9022-47FD-BF0B-FE4924AEB9BF}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.28515625" customWidth="1"/>
+    <col min="1" max="1" width="47.26953125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2760,7 +2854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>213</v>
       </c>
@@ -2768,7 +2862,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>215</v>
       </c>
@@ -2776,7 +2870,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>217</v>
       </c>
@@ -2787,7 +2881,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -2798,7 +2892,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -2809,7 +2903,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>224</v>
       </c>
@@ -2817,7 +2911,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>226</v>
       </c>
@@ -2825,7 +2919,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>227</v>
       </c>
@@ -2833,7 +2927,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>229</v>
       </c>
@@ -2841,7 +2935,167 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662F1AC-DC32-47FE-A439-717A16D5CC6B}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="16"/>
     </row>
   </sheetData>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1006" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29CD53C3-0C27-4D25-B6F4-15240A76266A}"/>
+  <xr:revisionPtr revIDLastSave="1124" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F53F454-F711-4B85-B303-D1608969B063}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1 Cylchedau Trydanol" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="3.5 Priodweddau Tonnau" sheetId="2" r:id="rId5"/>
     <sheet name="1.6 Adlewyrchiad mewnol cyflawn" sheetId="6" r:id="rId6"/>
     <sheet name="1.7 Tonnau Seismig" sheetId="7" r:id="rId7"/>
+    <sheet name="1.8 Damcaniaeth Ginetig" sheetId="8" r:id="rId8"/>
+    <sheet name="1.9 Electromagneteg" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="313">
   <si>
     <t>Cwestiwn</t>
   </si>
@@ -462,9 +464,6 @@
     <t>Rhestrwch ffynonellau egni adnewyddadwy</t>
   </si>
   <si>
-    <t>gwynt&lt;br&gt;solar&lt;br&gt;trydan dŵr&lt;br&gt;pŵer llanw&lt;br&gt;pŵer tonnau&lt;br&gt;biomas</t>
-  </si>
-  <si>
     <t>Beth yw ffynhonnell egni &lt;b&gt;anadnewyddadwy&lt;/b&gt;?</t>
   </si>
   <si>
@@ -878,13 +877,160 @@
     <t>Pam bod tonnau P yn cyrraedd bob gorsaf o flaen tonnau S?</t>
   </si>
   <si>
-    <t>Mae tonnau P yn gyflymch na tonnau S</t>
-  </si>
-  <si>
     <t>Pam bod y tonnau seismig yn cyrraedd gorsaf A cyn gorsaf B?</t>
   </si>
   <si>
     <t>Mae gorsaf A yn agosach i'r daeargryn na gorsaf B.</t>
+  </si>
+  <si>
+    <t>Mae tonnau P yn gyflymach na tonnau S</t>
+  </si>
+  <si>
+    <t>gwynt&lt;br&gt;solar&lt;br&gt;trydan dŵr&lt;br&gt;pŵer llanw&lt;br&gt;pŵer tonnau&lt;br&gt;biomas&lt;br&gt;geothermal</t>
+  </si>
+  <si>
+    <t>damcaniaeth_ginetig_cyfaint.png</t>
+  </si>
+  <si>
+    <t>Eglurwch pam mae'r gwasgedd yn cynyddu wrth i'r cyfaint leihau.</t>
+  </si>
+  <si>
+    <t>Beth yw uned grym?</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Beth yw uned arwynebedd?</t>
+  </si>
+  <si>
+    <t>m$^{2}$</t>
+  </si>
+  <si>
+    <t>Beth yw uned gwasgedd?</t>
+  </si>
+  <si>
+    <t>Pa neu N/m$^{2}$</t>
+  </si>
+  <si>
+    <t>damcaniaeth_ginetig_newidcyflwr.png</t>
+  </si>
+  <si>
+    <t>Eglurwch beth sy'n digwydd rhwng A a B.</t>
+  </si>
+  <si>
+    <t>Gronynnau'n mynd yn agosach at ei gilydd.&lt;br&gt;&lt;br&gt; Gwrthdaro yn fwy aml gyda waliau y cynhwysydd&lt;br&gt;&lt;br&gt;Mwy o wrthdrawiadau bob eiliad felly mwy o rym.</t>
+  </si>
+  <si>
+    <t>Eglurwch beth sy'n digwydd rhwng B a C</t>
+  </si>
+  <si>
+    <t>Eglurwch beth sy'n digwydd rhwng C a D.</t>
+  </si>
+  <si>
+    <t>Mae tymheredd y dŵr yn cynyddu&lt;br&gt;&lt;br&gt;Mae egni cinetig y moleciwlau’n cynyddu.</t>
+  </si>
+  <si>
+    <t>Eglurwch beth sy'n digwydd rhwng D ac E.</t>
+  </si>
+  <si>
+    <t>Mae'r dŵr yn anweddu (newid cyflwr o hylif i nwy). &lt;br&gt;&lt;br&gt; Mae'r tymheredd yn aros yn gyson felly mae'r egni sy'n cael ei gyflenwi yn torri bondiau rhwng y moleciwlau.</t>
+  </si>
+  <si>
+    <t>Mae'r iâ yn ymdoddi (newid cyflwr o solid i hylif). &lt;br&gt;&lt;br&gt; Mae'r tymheredd yn aros yn gyson felly mae'r egni sy'n cael ei gyflenwi yn torri bondiau rhwng y moleciwlau.</t>
+  </si>
+  <si>
+    <t>Eglurwch beth sy'n digwydd rhwng E ac F.</t>
+  </si>
+  <si>
+    <t>Mae tymheredd yr anwedd dŵr yn cynyddu&lt;br&gt;&lt;br&gt;Mae egni cinetig y moleciwlau’n cynyddu.</t>
+  </si>
+  <si>
+    <t>Eglurwch pam mae gwasgedd nwy yn cynyddu wrth i'r tymheredd gynyddu os yw'r cyfaint yn aros yn gyson.</t>
+  </si>
+  <si>
+    <t>nifer o wrthdrawiadau bob eiliad yn cynyddu</t>
+  </si>
+  <si>
+    <t>Mae’r gronynnau yn symud yn gyflymach. &lt;br&gt;&lt;br&gt; gronynnau yn gwrthdaro yn fwy aml gyda waliau y cynhwysydd&lt;br&gt;&lt;br&gt;Mwy o wrthdrawiadau bob eiliad felly mwy o rym.</t>
+  </si>
+  <si>
+    <t>electromagneteg_generadur.png</t>
+  </si>
+  <si>
+    <t>I ba gyfeiriad mae'r maes magnetig yn gweithredu?</t>
+  </si>
+  <si>
+    <t>I ba gyfeiriad mae'r mae ochr dde'r coil yn symud?</t>
+  </si>
+  <si>
+    <t>I ba gyfeiriad mae'r cerrynt sy'n cael ei anwytho yn ochr dde'r coil?</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Esboniwch pam mae cerrynt yn cael ei anwytho (gynhyrchu) yn y coil wrth iddo gylchdroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mae'r coil yn &lt;b&gt;torri&lt;/b&gt; drwy &lt;b&gt; llinellau maes magnetig&lt;/b&gt; </t>
+  </si>
+  <si>
+    <t>Esboniwch sut mae newidydd yn gweithio</t>
+  </si>
+  <si>
+    <t>Mae cerrynt eiledol yn y coil cynradd yn cynhyrchu maes magnetig newidiol.&lt;br&gt;&lt;br&gt;Mae maes magnetig newidiol yn cael ei gynhyrchu yn y craidd haearn hefyd&lt;br&gt;&lt;br&gt; Mae'r craidd haearn yn cysylltu'r maes magnetig newidiol gyda'r coil eilaidd&lt;br&gt;&lt;br&gt; Mae hyn yn anwytho foltedd eiledol ar draws y coil eilaidd.</t>
+  </si>
+  <si>
+    <t>Esboniwch pam bod angen foltedd c.e. Gyda newidyddion</t>
+  </si>
+  <si>
+    <t>Mae foltedd c.e. yn creu maes magnetig newidiol.</t>
+  </si>
+  <si>
+    <t>electromagneteg_allbwn_generadur.png</t>
+  </si>
+  <si>
+    <t>Rhesrwch dri peth fysa'n cynyddu y foltedd allbwn.</t>
+  </si>
+  <si>
+    <t>Magnetau cryfach&lt;br&gt;&lt;br&gt; coil yn troelli'n fwy cyflym&lt;br&gt;&lt;br&gt; mwy o droadau ar y coil</t>
+  </si>
+  <si>
+    <t>Sut mae cynyddu amledd foltedd allbwn generadur?</t>
+  </si>
+  <si>
+    <t>coil yn troelli'n fwy cyflym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetau cryfach&lt;br&gt;&lt;br&gt; cynyddu'r cerrynt drwyr coil.&lt;br&gt;&lt;br&gt; </t>
+  </si>
+  <si>
+    <t>Nodwch tair ffordd o wneud i'r modur droelli'n gyflymach</t>
+  </si>
+  <si>
+    <t>electromagneteg_modur.png</t>
+  </si>
+  <si>
+    <t>electromagneteg_maesgwifren.png</t>
+  </si>
+  <si>
+    <t>Pa ddiagram sy’n dangos yn gywir beth yw patrwm y maes magnetig o amgylch gwifren syth sy’n cario cerrynt?</t>
+  </si>
+  <si>
+    <t>diagram A</t>
+  </si>
+  <si>
+    <t>Pa reol allwch ddefnyddio i ddarganfod cyfeiriad grym ar wifren/coil sydd yn cario cerrynt  mewn maes magnetig?</t>
+  </si>
+  <si>
+    <t>Pa reol allwch ddefnyddio i ddarganfod cyfeiriad y cerrynt  mewn coil sydd yn cylchdroi tu mewn i faes magnetig?</t>
+  </si>
+  <si>
+    <t>Rheol Llaw Dde Fleming</t>
+  </si>
+  <si>
+    <t>Rheol Llaw Chwith Fleming</t>
   </si>
 </sst>
 </file>
@@ -1583,10 +1729,10 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -1626,7 +1772,7 @@
         <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1636,27 +1782,27 @@
         <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1673,124 +1819,124 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>134</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>136</v>
       </c>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>148</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>149</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
@@ -1893,122 +2039,122 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2177,149 +2323,149 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>208</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>209</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>210</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -2856,83 +3002,83 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
         <v>213</v>
-      </c>
-      <c r="B2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" t="s">
         <v>215</v>
-      </c>
-      <c r="B3" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" t="s">
         <v>217</v>
-      </c>
-      <c r="B4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" t="s">
         <v>220</v>
       </c>
-      <c r="B5" t="s">
-        <v>221</v>
-      </c>
       <c r="C5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" t="s">
         <v>222</v>
       </c>
-      <c r="B6" t="s">
-        <v>223</v>
-      </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>224</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2970,133 +3116,502 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" t="s">
         <v>234</v>
-      </c>
-      <c r="B2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" t="s">
         <v>237</v>
-      </c>
-      <c r="B4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
         <v>239</v>
-      </c>
-      <c r="B5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
         <v>241</v>
-      </c>
-      <c r="B6" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>248</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>254</v>
-      </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>256</v>
-      </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3845283-C739-407E-8C4D-187BEC5001FF}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACE78C2-2B98-4BFC-8521-23D1103289B3}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="16"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="16"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CardiauFflachFfisegbl10.xlsx
+++ b/CardiauFflachFfisegbl10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hwbwave15-my.sharepoint.com/personal/griffithsr144_hwbcymru_net/Documents/cardiau fflach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1124" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F53F454-F711-4B85-B303-D1608969B063}"/>
+  <xr:revisionPtr revIDLastSave="1126" documentId="8_{063AF45C-C4AD-4E4D-BA54-412CED646CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7F09675-6C52-4313-81F8-03E9A539285E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -982,9 +982,6 @@
     <t>Mae cerrynt eiledol yn y coil cynradd yn cynhyrchu maes magnetig newidiol.&lt;br&gt;&lt;br&gt;Mae maes magnetig newidiol yn cael ei gynhyrchu yn y craidd haearn hefyd&lt;br&gt;&lt;br&gt; Mae'r craidd haearn yn cysylltu'r maes magnetig newidiol gyda'r coil eilaidd&lt;br&gt;&lt;br&gt; Mae hyn yn anwytho foltedd eiledol ar draws y coil eilaidd.</t>
   </si>
   <si>
-    <t>Esboniwch pam bod angen foltedd c.e. Gyda newidyddion</t>
-  </si>
-  <si>
     <t>Mae foltedd c.e. yn creu maes magnetig newidiol.</t>
   </si>
   <si>
@@ -1003,9 +1000,6 @@
     <t>coil yn troelli'n fwy cyflym</t>
   </si>
   <si>
-    <t xml:space="preserve">Magnetau cryfach&lt;br&gt;&lt;br&gt; cynyddu'r cerrynt drwyr coil.&lt;br&gt;&lt;br&gt; </t>
-  </si>
-  <si>
     <t>Nodwch tair ffordd o wneud i'r modur droelli'n gyflymach</t>
   </si>
   <si>
@@ -1031,6 +1025,12 @@
   </si>
   <si>
     <t>Rheol Llaw Chwith Fleming</t>
+  </si>
+  <si>
+    <t>Magnetau cryfach&lt;br&gt;&lt;br&gt; cynyddu'r cerrynt drwyr coil.&lt;br&gt;&lt;br&gt;mwy o droadau ar y coil</t>
+  </si>
+  <si>
+    <t>Esboniwch pam bod angen foltedd c.e. gyda newidyddion</t>
   </si>
 </sst>
 </file>
@@ -1447,13 +1447,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>74</v>
       </c>
@@ -1487,7 +1487,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>76</v>
       </c>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>109</v>
       </c>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>82</v>
       </c>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>82</v>
       </c>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>82</v>
       </c>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>82</v>
       </c>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>82</v>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>82</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>82</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>111</v>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>110</v>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>78</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>85</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>88</v>
       </c>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>94</v>
       </c>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>95</v>
       </c>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>121</v>
       </c>
@@ -1719,7 +1719,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>122</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>231</v>
       </c>
@@ -1747,13 +1747,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>125</v>
       </c>
@@ -1777,7 +1777,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
@@ -1787,7 +1787,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>127</v>
       </c>
@@ -1797,7 +1797,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>128</v>
       </c>
@@ -1807,7 +1807,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>130</v>
       </c>
@@ -1827,7 +1827,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>132</v>
       </c>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>134</v>
       </c>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>136</v>
       </c>
@@ -1855,7 +1855,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>137</v>
       </c>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>139</v>
       </c>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>147</v>
       </c>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>149</v>
       </c>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>141</v>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>142</v>
       </c>
@@ -1911,7 +1911,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>145</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>152</v>
       </c>
@@ -1931,7 +1931,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>153</v>
       </c>
@@ -1941,67 +1941,67 @@
       <c r="C19" s="4"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="14"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14"/>
       <c r="B24" s="7"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="7"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="9"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="9"/>
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="9"/>
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="9"/>
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="9"/>
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="9"/>
     </row>
@@ -2017,13 +2017,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>162</v>
       </c>
@@ -2047,7 +2047,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>164</v>
       </c>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>164</v>
       </c>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>164</v>
       </c>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>166</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>170</v>
       </c>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>169</v>
       </c>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>172</v>
       </c>
@@ -2129,7 +2129,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>161</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>173</v>
       </c>
@@ -2149,7 +2149,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>175</v>
       </c>
@@ -2159,133 +2159,133 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="15"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="15"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="15"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="7"/>
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="15"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="6"/>
       <c r="C20" s="4"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="6"/>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="7"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="7"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="9"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="9"/>
       <c r="C32" s="4"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
     </row>
@@ -2301,13 +2301,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>182</v>
       </c>
@@ -2331,7 +2331,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>196</v>
       </c>
@@ -2341,7 +2341,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>198</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>184</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>186</v>
       </c>
@@ -2371,7 +2371,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>187</v>
       </c>
@@ -2381,7 +2381,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>194</v>
       </c>
@@ -2391,7 +2391,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>191</v>
       </c>
@@ -2401,7 +2401,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>192</v>
       </c>
@@ -2411,7 +2411,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>200</v>
       </c>
@@ -2431,7 +2431,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>201</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>203</v>
       </c>
@@ -2451,7 +2451,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>206</v>
       </c>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>208</v>
       </c>
@@ -2469,123 +2469,123 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="15"/>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="7"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="15"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="6"/>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="6"/>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="7"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="7"/>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="9"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="9"/>
       <c r="C34" s="4"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="9"/>
       <c r="C35" s="4"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="9"/>
       <c r="C36" s="4"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="9"/>
       <c r="C37" s="4"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="9"/>
     </row>
@@ -2601,13 +2601,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="57.54296875" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="57.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -2770,7 +2770,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>49</v>
       </c>
@@ -2780,7 +2780,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
@@ -2838,7 +2838,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>69</v>
       </c>
@@ -2848,7 +2848,7 @@
       <c r="C24" s="4"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="C25" s="4"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>35</v>
       </c>
@@ -2868,7 +2868,7 @@
       <c r="C26" s="4"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>55</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="C27" s="4"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>56</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="C28" s="4"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>57</v>
       </c>
@@ -2898,7 +2898,7 @@
       <c r="C29" s="4"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>58</v>
       </c>
@@ -2908,7 +2908,7 @@
       <c r="C30" s="4"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>59</v>
       </c>
@@ -2918,7 +2918,7 @@
       <c r="C31" s="4"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>70</v>
       </c>
@@ -2935,39 +2935,39 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10"/>
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>
@@ -2980,13 +2980,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33D1AC1-9022-47FD-BF0B-FE4924AEB9BF}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>212</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>214</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>216</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>219</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>221</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>223</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>225</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>226</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>228</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" s="16"/>
     </row>
   </sheetData>
@@ -3093,14 +3093,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1662F1AC-DC32-47FE-A439-717A16D5CC6B}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>242</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>236</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>238</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>240</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>243</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>246</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>247</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>251</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>252</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>254</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>258</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>260</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>261</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16" s="16"/>
     </row>
   </sheetData>
@@ -3253,14 +3253,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3845283-C739-407E-8C4D-187BEC5001FF}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>267</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>269</v>
       </c>
@@ -3294,7 +3294,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>271</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>266</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>284</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>274</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>276</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>277</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>279</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>282</v>
       </c>
@@ -3378,37 +3378,37 @@
         <v>273</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" s="16"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B13" s="16"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="16"/>
     </row>
   </sheetData>
@@ -3420,14 +3420,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACE78C2-2B98-4BFC-8521-23D1103289B3}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.26953125" customWidth="1"/>
+    <col min="1" max="1" width="47.28515625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3441,51 +3441,51 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>305</v>
-      </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>288</v>
       </c>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>289</v>
       </c>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>290</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>292</v>
       </c>
@@ -3529,29 +3529,29 @@
       </c>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="B11" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>294</v>
       </c>
@@ -3560,57 +3560,57 @@
       </c>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" s="16"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="16"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B25" s="16"/>
     </row>
   </sheetData>
